--- a/registre_licences_clubs.xlsx
+++ b/registre_licences_clubs.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licences Clubs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accès Staff &amp; Support" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,69 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <b val="1"/>
-      <color rgb="00B45309"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <b val="1"/>
-      <color rgb="000A1728"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="0015803D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <b val="1"/>
-      <color rgb="0015803D"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000A1728"/>
-        <bgColor rgb="000A1728"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-        <bgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -101,66 +46,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00E2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E2E8F0"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,463 +425,218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nom de l'Espace / Club</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>N° FFF / Réf</t>
+          <t>Code_FFF</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Clé de Licence Cryptographique</t>
+          <t>Cle_Licence</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Type de Licence</t>
+          <t>Statut</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Comptes Staff Actifs</t>
+          <t>Nb_Comptes_Staff</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Date Émission</t>
+          <t>Lien_Activation</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Lien Direct d'Activation PWA</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Fichier QR Code</t>
+          <t>Fichier_QR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Master Direction (Nino)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>MASTER_NINO</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>MD-MASTER-NINO-2026</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Super-Admin (Accès Global)</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://match-day-app.netlify.app/?key=MD-MASTER-NINO-2026</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>qr_root.png</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ES Genech</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>525674</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>MD-GNCH-88F4-A92B</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Partenaire Officiel VIP (Illimité)</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://match-day-app.netlify.app/?key=MD-GNCH-88F4-A92B</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>qr_gnch.png</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>FC Seclin</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>500934</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>MD-SCLN-74C2-91E3</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Version d'Évaluation (Bridée)</t>
         </is>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>https://match-day-app.netlify.app/?key=MD-SCLN-74C2-91E3</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>qr_scln.png</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>FC Bondues</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>500123</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>MD-BNDS-55D1-82A4</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>En attente (Devis Club)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>https://match-day-app.netlify.app/?key=MD-BNDS-55D1-82A4</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>qr_bnds.png</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Club Partenaire</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Code Support Staff</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Rôle / Titulaire Déclaré</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Statut Accès</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Première Connexion</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Dernière Activité</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Comment Nino Identifie en Support</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Master Direction (Nino)</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>#ROOT-01</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>Nino F. (Super-Admin / Direction SaaS)</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>Actif</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28 09:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-28 13:30</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Si problème, le coach donne #ROOT-01 à Nino</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>ES Genech</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>#GN-01</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>Entraîneur Principal - Séniors A</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>Actif</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-28 10:15</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-28 13:10</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Si problème, le coach donne #GN-01 à Nino</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>ES Genech</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>#GN-02</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>Entraîneur Adjoint &amp; Préparateur</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>Actif</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-28 10:30</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-28 12:45</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Si problème, le coach donne #GN-02 à Nino</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>ES Genech</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>#GN-03</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Président &amp; Comité Directeur</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>Actif</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-28 11:00</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-28 12:30</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Si problème, le coach donne #GN-03 à Nino</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>US Lesquin</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>500426</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MD-LSQN-92D3-71B8</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Version d'Évaluation (Bridée)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://match-day-app.netlify.app/?key=MD-LSQN-92D3-71B8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>qr_lsqn.png</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>FC Seclin</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>#SC-01</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Coach Séniors A (Staff R2)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>Actif</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-28 11:10</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-28 12:55</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Si problème, le coach donne #SC-01 à Nino</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FC Bondues</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>500123</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MD-BNDS-55D1-82A4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>En attente (Devis Club)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://match-day-app.netlify.app/?key=MD-BNDS-55D1-82A4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>qr_bnds.png</t>
         </is>
       </c>
     </row>
